--- a/public/slagging_data.xlsx
+++ b/public/slagging_data.xlsx
@@ -86,39 +86,15 @@
     <t>Sulphur (S)</t>
   </si>
   <si>
-    <t>SiO2</t>
-  </si>
-  <si>
-    <t>Al2O3</t>
-  </si>
-  <si>
-    <t>Fe2O3</t>
-  </si>
-  <si>
     <t>CaO</t>
   </si>
   <si>
     <t>MgO</t>
   </si>
   <si>
-    <t>Na2O</t>
-  </si>
-  <si>
-    <t>TiO2</t>
-  </si>
-  <si>
-    <t>SO3</t>
-  </si>
-  <si>
-    <t>P2O5</t>
-  </si>
-  <si>
     <t>Coal</t>
   </si>
   <si>
-    <t>MN3O4</t>
-  </si>
-  <si>
     <t>Hemispherical Temp.</t>
   </si>
   <si>
@@ -131,7 +107,31 @@
     <t>Fluid Temp.</t>
   </si>
   <si>
-    <t>K2O</t>
+    <t>Mn₃O₄</t>
+  </si>
+  <si>
+    <t>P₂O₅</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SO₃ </t>
+  </si>
+  <si>
+    <t>TiO₂</t>
+  </si>
+  <si>
+    <t>K₂O</t>
+  </si>
+  <si>
+    <t>Fe₂O₃</t>
+  </si>
+  <si>
+    <t>Na₂O</t>
+  </si>
+  <si>
+    <t>Al₂O₃</t>
+  </si>
+  <si>
+    <t>SiO₂</t>
   </si>
 </sst>
 </file>
@@ -491,7 +491,7 @@
   <sheetData>
     <row r="2" spans="1:22" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>14</v>
@@ -512,49 +512,49 @@
         <v>19</v>
       </c>
       <c r="H2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>24</v>
-      </c>
       <c r="M2" s="1" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="Q2" s="1" t="s">
         <v>28</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="V2" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
@@ -1512,5 +1512,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>